--- a/OUTPUT_FOLDER/Full_statement_2026-03-22.xlsx
+++ b/OUTPUT_FOLDER/Full_statement_2026-03-22.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI-Driven-Expense-Tracker-Public\OUTPUT_FOLDER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D97969F-5733-403E-8FD5-B8E9DC63A747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89AF140-D295-4EC3-8655-04185256EFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transactions" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="121">
   <si>
     <t>S.No</t>
   </si>
@@ -384,37 +384,10 @@
     <t>lending</t>
   </si>
   <si>
-    <t>UPI/DR/612624205285/Bank Acco/ICIC/**1601905185/Payment //YBL422cb92195a247b590ed03f3bf27eff5/06/03/2026 18:09:48</t>
-  </si>
-  <si>
-    <t>4,000.00</t>
-  </si>
-  <si>
-    <t>UPI IN/607418966073/9629236207@naviaxis/Paid/0000</t>
-  </si>
-  <si>
-    <t>5,000.00</t>
-  </si>
-  <si>
     <t>13/03/26</t>
   </si>
   <si>
-    <t>UPI-NAGENDRAPRASATH M-PRASATHNAGENDRA8-1@OKICICI-KVBL0001853-643851461988-UPI</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
     <t>15/03/26</t>
-  </si>
-  <si>
-    <t>UPI-NAGENDRAPRASATH MUTH-9629236207-2@NYES-FDRL0001441-607418966073-PAID VIA NAVI UPI</t>
-  </si>
-  <si>
-    <t>UPI-CR-442993318153-KARTHICK M-TMBL-077100050308214-Payment from PhonePe</t>
-  </si>
-  <si>
-    <t>UPI-CR-643851461988-NAGENDRAPRASATH MUTHUKUMAR-HDFC-50100509133930-UPI</t>
   </si>
 </sst>
 </file>
@@ -4302,12 +4275,8 @@
       <c r="A2" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>120</v>
-      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
       <c r="D2" s="23"/>
       <c r="E2" s="23" t="s">
         <v>11</v>
@@ -4317,27 +4286,19 @@
       <c r="A3" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>121</v>
-      </c>
+      <c r="B3" s="24"/>
       <c r="C3" s="24"/>
-      <c r="D3" s="24" t="s">
-        <v>122</v>
-      </c>
+      <c r="D3" s="24"/>
       <c r="E3" s="24" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>125</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="23"/>
       <c r="E4" s="23" t="s">
         <v>27</v>
@@ -4345,14 +4306,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>125</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="24"/>
       <c r="E5" s="24" t="s">
         <v>27</v>
@@ -4362,13 +4319,9 @@
       <c r="A6" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="23" t="s">
-        <v>128</v>
-      </c>
+      <c r="B6" s="23"/>
       <c r="C6" s="23"/>
-      <c r="D6" s="23" t="s">
-        <v>120</v>
-      </c>
+      <c r="D6" s="23"/>
       <c r="E6" s="23" t="s">
         <v>13</v>
       </c>
@@ -4377,13 +4330,9 @@
       <c r="A7" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="24" t="s">
-        <v>129</v>
-      </c>
+      <c r="B7" s="24"/>
       <c r="C7" s="24"/>
-      <c r="D7" s="24" t="s">
-        <v>122</v>
-      </c>
+      <c r="D7" s="24"/>
       <c r="E7" s="24" t="s">
         <v>13</v>
       </c>
